--- a/docs/databricks/healthcare_claims_schema.xlsx
+++ b/docs/databricks/healthcare_claims_schema.xlsx
@@ -560,7 +560,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Catalog: hive_metastore  |  Schema: healthcare_claims  |  Source: sample/demo data (no Databricks credentials found)  |  Generated: 2026-03-09 06:21:24 UTC</t>
+          <t>Catalog: hive_metastore  |  Schema: healthcare_claims  |  Source: sample/demo data (no Databricks credentials found)  |  Generated: 2026-03-09 06:22:37 UTC</t>
         </is>
       </c>
     </row>
